--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
         <v>4.6</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.13</v>
+        <v>2.05</v>
       </c>
       <c r="M58" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.05</v>
+        <v>1.13</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="N59" t="n">
-        <v>3.3</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD59" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.85</v>
+        <v>1.88</v>
       </c>
       <c r="M77" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N77" t="n">
-        <v>2.35</v>
+        <v>3.85</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N78" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N79" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N80" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="M81" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N81" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="M82" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N82" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.05</v>
+        <v>1.13</v>
       </c>
       <c r="M58" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.3</v>
+        <v>22</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="M78" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="M80" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N80" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="M81" t="n">
         <v>3.55</v>
       </c>
       <c r="N81" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N82" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M83" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N83" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.88</v>
+        <v>2.85</v>
       </c>
       <c r="M77" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N77" t="n">
-        <v>3.85</v>
+        <v>2.35</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="M79" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N79" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="M80" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N80" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="M81" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N81" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="M82" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N82" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M83" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N83" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G94" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7612,10 +7612,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="M77" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N77" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M78" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="M79" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N79" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="M82" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="M83" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N83" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M54" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="M77" t="n">
         <v>3.55</v>
       </c>
       <c r="N77" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.1</v>
+        <v>3.55</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="M80" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N80" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="M81" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N82" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.55</v>
+        <v>1.88</v>
       </c>
       <c r="M83" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N83" t="n">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G92" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.05</v>
+        <v>1.13</v>
       </c>
       <c r="M58" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.3</v>
+        <v>22</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.13</v>
+        <v>2.05</v>
       </c>
       <c r="M60" t="n">
-        <v>7.3</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>22</v>
+        <v>3.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>5.05</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>4.06</v>
+        <v>3.35</v>
       </c>
       <c r="N72" t="n">
-        <v>1.64</v>
+        <v>3.75</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="M77" t="n">
         <v>3.55</v>
       </c>
       <c r="N77" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.55</v>
+        <v>2.12</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N79" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="M80" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N80" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N81" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,55 +10179,55 @@
         </is>
       </c>
       <c r="L82" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB82" t="n">
         <v>1.75</v>
-      </c>
-      <c r="M82" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N82" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="M83" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N83" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G92" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
         <v>4.4</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M53" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="M72" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB72" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="M77" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N77" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="M78" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N78" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="M79" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N79" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="M80" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N80" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="M81" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.61</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>2.61</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.49</v>
+        <v>2.49</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.05</v>
+        <v>5.7</v>
       </c>
       <c r="M71" t="n">
-        <v>4.06</v>
+        <v>4.15</v>
       </c>
       <c r="N71" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="M77" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N77" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.88</v>
+        <v>3.55</v>
       </c>
       <c r="M78" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N78" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N79" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="M80" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N80" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N81" t="n">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="M83" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N83" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>6.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="M77" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N77" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M78" t="n">
         <v>3.55</v>
       </c>
-      <c r="M78" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N78" t="n">
-        <v>2.05</v>
+        <v>4.6</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M79" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N79" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="M80" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="N80" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="M81" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N82" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3994,10 +3994,10 @@
         <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="N54" t="n">
         <v>4.8</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="M55" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="N55" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8394,7 +8394,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M67" t="n">
         <v>5</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M70" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="N70" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N76" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="M77" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N77" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="N78" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="N79" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="M80" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
         <v>3.85</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,55 +10060,55 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="N81" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
         <v>2.35</v>
       </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="M83" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N83" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10658,10 +10658,10 @@
         <v>2.15</v>
       </c>
       <c r="M86" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="N86" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
         <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11134,10 +11134,10 @@
         <v>1.85</v>
       </c>
       <c r="M90" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="N90" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4589,10 +4589,10 @@
         <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="N35" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.85</v>
+        <v>2.49</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>3.65</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.42</v>
+        <v>2.03</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6017,10 +6017,10 @@
         <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.49</v>
+        <v>3.05</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M60" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N60" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD60" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M76" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="M77" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N77" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="M79" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="M81" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>3.36</v>
+        <v>1.88</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.56</v>
+        <v>2.05</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N82" t="n">
-        <v>1.88</v>
+        <v>3.36</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="M83" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
         <v>4.4</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
         <v>4.4</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>3.85</v>
       </c>
       <c r="M35" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="M36" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.85</v>
+        <v>2.49</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.49</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>6.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M42" t="n">
         <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>1.97</v>
+        <v>3.65</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.03</v>
+        <v>3.9</v>
       </c>
       <c r="M45" t="n">
         <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>6.4</v>
+        <v>2.25</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.05</v>
+        <v>1.42</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.25</v>
+        <v>7.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="M77" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="N77" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="M78" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="N78" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="M79" t="n">
         <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M82" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>3.36</v>
+        <v>2.98</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M83" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N83" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1974,7 +1974,7 @@
         <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2093,7 +2093,7 @@
         <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
         <v>4.4</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.02</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.85</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M42" t="n">
         <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>1.97</v>
+        <v>4.5</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="M46" t="n">
         <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M48" t="n">
         <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="M53" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>7.3</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>22</v>
+        <v>3.47</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>5.7</v>
       </c>
       <c r="M68" t="n">
-        <v>3.27</v>
+        <v>4.15</v>
       </c>
       <c r="N68" t="n">
-        <v>3.62</v>
+        <v>1.58</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="M71" t="n">
-        <v>4.15</v>
+        <v>3.27</v>
       </c>
       <c r="N71" t="n">
-        <v>1.58</v>
+        <v>3.62</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="N77" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="M78" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="N78" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="M79" t="n">
         <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="M82" t="n">
         <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="M83" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="N83" t="n">
-        <v>3.36</v>
+        <v>2.92</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1974,7 +1974,7 @@
         <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2093,7 +2093,7 @@
         <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
         <v>4.4</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
         <v>4.4</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.65</v>
+        <v>6.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.42</v>
+        <v>2.03</v>
       </c>
       <c r="M42" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.85</v>
+        <v>1.42</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.49</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.75</v>
+        <v>6.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.4</v>
+        <v>2.49</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>6.9</v>
+        <v>2.75</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>3.65</v>
+        <v>1.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M37" t="n">
         <v>3.85</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N37" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.7</v>
+        <v>1.49</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N41" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.9</v>
+        <v>1.42</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N43" t="n">
-        <v>1.97</v>
+        <v>7.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.42</v>
+        <v>3.9</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>7.4</v>
+        <v>1.97</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.49</v>
+        <v>3.05</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="M55" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="N55" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M60" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N60" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD60" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.05</v>
+        <v>5.7</v>
       </c>
       <c r="M71" t="n">
-        <v>3.27</v>
+        <v>4.15</v>
       </c>
       <c r="N71" t="n">
-        <v>3.62</v>
+        <v>1.58</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="M77" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="N77" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="M78" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="N78" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="M79" t="n">
         <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="M80" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N80" t="n">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.56</v>
+        <v>2.65</v>
       </c>
       <c r="M81" t="n">
         <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="M82" t="n">
         <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M83" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N83" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1974,7 +1974,7 @@
         <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2093,7 +2093,7 @@
         <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.85</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
         <v>4.4</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.85</v>
+        <v>2.49</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="M37" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.49</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>7.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.49</v>
+        <v>3.9</v>
       </c>
       <c r="M41" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>1.97</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.42</v>
+        <v>2.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>7.4</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>1.97</v>
+        <v>6.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="N55" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>7.3</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>22</v>
+        <v>3.47</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="M71" t="n">
-        <v>4.15</v>
+        <v>3.27</v>
       </c>
       <c r="N71" t="n">
-        <v>1.58</v>
+        <v>3.62</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.73</v>
+        <v>5.7</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="N72" t="n">
-        <v>4.4</v>
+        <v>1.58</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.06</v>
+        <v>2.65</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.49</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>6.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.8</v>
+        <v>3.85</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.9</v>
+        <v>2.61</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N41" t="n">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="N44" t="n">
-        <v>6.1</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N45" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>1.39</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.5</v>
+        <v>2.49</v>
       </c>
       <c r="M47" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N47" t="n">
-        <v>6.4</v>
+        <v>2.75</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N56" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.05</v>
+        <v>5.7</v>
       </c>
       <c r="M71" t="n">
-        <v>3.27</v>
+        <v>4.15</v>
       </c>
       <c r="N71" t="n">
-        <v>3.62</v>
+        <v>1.58</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="M72" t="n">
-        <v>4.15</v>
+        <v>3.27</v>
       </c>
       <c r="N72" t="n">
-        <v>1.58</v>
+        <v>3.62</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="N77" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="M78" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N78" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N79" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="M80" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="N80" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.06</v>
+        <v>3.56</v>
       </c>
       <c r="M81" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>2.98</v>
+        <v>1.88</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.56</v>
+        <v>2.06</v>
       </c>
       <c r="M83" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>1.88</v>
+        <v>2.98</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11250,7 +11250,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="M91" t="n">
         <v>3.1</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
         <v>4.4</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>6.9</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>3.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.85</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.9</v>
+        <v>6.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="M51" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="N51" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="M71" t="n">
-        <v>4.15</v>
+        <v>3.27</v>
       </c>
       <c r="N71" t="n">
-        <v>1.58</v>
+        <v>3.62</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.05</v>
+        <v>5.7</v>
       </c>
       <c r="M72" t="n">
-        <v>3.27</v>
+        <v>4.15</v>
       </c>
       <c r="N72" t="n">
-        <v>3.62</v>
+        <v>1.58</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M76" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="M77" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="N77" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.78</v>
+        <v>2.34</v>
       </c>
       <c r="M78" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N78" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M79" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>3.36</v>
+        <v>2.98</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="M80" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.56</v>
+        <v>2.65</v>
       </c>
       <c r="M81" t="n">
         <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.65</v>
+        <v>3.56</v>
       </c>
       <c r="M82" t="n">
         <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M83" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N83" t="n">
-        <v>2.98</v>
+        <v>3.36</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N91" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M92" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="N13" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
         <v>4.4</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.69</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="N32" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>6.1</v>
+        <v>1.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="N37" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>2.61</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>3.09</v>
       </c>
       <c r="N38" t="n">
-        <v>6.4</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.75</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.19</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>1.85</v>
+        <v>6.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.61</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
-        <v>3.09</v>
+        <v>4.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2.42</v>
+        <v>6.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.49</v>
+        <v>3.85</v>
       </c>
       <c r="M49" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>1.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,14 +6609,14 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.05</v>
+        <v>2.03</v>
       </c>
       <c r="M52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N52" t="n">
         <v>3.4</v>
       </c>
-      <c r="N52" t="n">
-        <v>2.25</v>
-      </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.05</v>
+        <v>5.7</v>
       </c>
       <c r="M71" t="n">
-        <v>3.27</v>
+        <v>4.15</v>
       </c>
       <c r="N71" t="n">
-        <v>3.62</v>
+        <v>1.58</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M74" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N74" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.22</v>
+        <v>2.78</v>
       </c>
       <c r="M76" t="n">
-        <v>5.8</v>
+        <v>3.41</v>
       </c>
       <c r="N76" t="n">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="M78" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N78" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N79" t="n">
-        <v>2.98</v>
+        <v>3.36</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.65</v>
+        <v>3.56</v>
       </c>
       <c r="M81" t="n">
         <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N82" t="n">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M83" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>3.36</v>
+        <v>2.98</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
         <v>4.4</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.75</v>
+        <v>2.49</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.69</v>
+        <v>2.61</v>
       </c>
       <c r="M37" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.61</v>
+        <v>1.69</v>
       </c>
       <c r="M38" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N50" t="n">
-        <v>2.25</v>
+        <v>6.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N52" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="M54" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="N55" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>7.3</v>
+        <v>3.85</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>3.47</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="M79" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="M80" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N80" t="n">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.61</v>
+        <v>1.49</v>
       </c>
       <c r="M37" t="n">
-        <v>3.09</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.05</v>
+        <v>2.61</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.03</v>
+        <v>3.75</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.85</v>
+        <v>1.5</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.5</v>
+        <v>3.85</v>
       </c>
       <c r="M50" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="M51" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="N51" t="n">
-        <v>6.9</v>
+        <v>4.5</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="M52" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>6.1</v>
+        <v>2.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="N54" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="M55" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="N55" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M58" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.73</v>
+        <v>5.7</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="N70" t="n">
-        <v>4.4</v>
+        <v>1.58</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="M71" t="n">
-        <v>4.15</v>
+        <v>3.27</v>
       </c>
       <c r="N71" t="n">
-        <v>1.58</v>
+        <v>3.62</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.22</v>
+        <v>2.78</v>
       </c>
       <c r="M74" t="n">
-        <v>5.8</v>
+        <v>3.41</v>
       </c>
       <c r="N74" t="n">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>3.56</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="M78" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M80" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
-        <v>3.36</v>
+        <v>2.98</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N81" t="n">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="N82" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M83" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N83" t="n">
-        <v>2.98</v>
+        <v>3.36</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G88" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.03</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.61</v>
+        <v>1.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.09</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.42</v>
+        <v>6.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5779,10 +5779,10 @@
         <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="N45" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="M46" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="N46" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.75</v>
+        <v>2.03</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M60" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N60" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD60" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M74" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N74" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N77" t="n">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N78" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="M79" t="n">
         <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>3.85</v>
+        <v>2.98</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N80" t="n">
-        <v>2.98</v>
+        <v>3.36</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M81" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="M82" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="M83" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="N83" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="N14" t="n">
-        <v>4.85</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
         <v>4.4</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>2.61</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.09</v>
       </c>
       <c r="N41" t="n">
-        <v>6.4</v>
+        <v>2.42</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.75</v>
+        <v>1.69</v>
       </c>
       <c r="M42" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="N42" t="n">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
       <c r="M43" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.97</v>
+        <v>1.62</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.19</v>
       </c>
       <c r="N44" t="n">
-        <v>6.9</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M45" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="N45" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.01</v>
+        <v>1.74</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="M46" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
       <c r="N46" t="n">
-        <v>6.1</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.85</v>
+        <v>1.53</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N50" t="n">
-        <v>1.9</v>
+        <v>6.2</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB50" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.65</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="M51" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.8</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="M70" t="n">
-        <v>4.15</v>
+        <v>3.27</v>
       </c>
       <c r="N70" t="n">
-        <v>1.58</v>
+        <v>3.62</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.05</v>
+        <v>5.2</v>
       </c>
       <c r="M71" t="n">
-        <v>3.27</v>
+        <v>4.3</v>
       </c>
       <c r="N71" t="n">
-        <v>3.62</v>
+        <v>1.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M77" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="M78" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>3.85</v>
+        <v>2.3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="M80" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="N80" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>1.88</v>
+        <v>3.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N82" t="n">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="M83" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.02</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.61</v>
+        <v>1.69</v>
       </c>
       <c r="M41" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.69</v>
+        <v>2.61</v>
       </c>
       <c r="M42" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.75</v>
+        <v>1.53</v>
       </c>
       <c r="M44" t="n">
-        <v>3.19</v>
+        <v>4.2</v>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.53</v>
+        <v>3.75</v>
       </c>
       <c r="M50" t="n">
-        <v>4.2</v>
+        <v>3.19</v>
       </c>
       <c r="N50" t="n">
-        <v>6.2</v>
+        <v>1.85</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.73</v>
+        <v>5.2</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N69" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.22</v>
+        <v>2.78</v>
       </c>
       <c r="M73" t="n">
-        <v>5.8</v>
+        <v>3.41</v>
       </c>
       <c r="N73" t="n">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M76" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N77" t="n">
-        <v>1.88</v>
+        <v>3.85</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N79" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="M80" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M81" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N81" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="N82" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M83" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N83" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
         <v>4.4</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.69</v>
+        <v>2.61</v>
       </c>
       <c r="M41" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.61</v>
+        <v>1.69</v>
       </c>
       <c r="M42" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="N42" t="n">
-        <v>2.42</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="M44" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,55 +6252,55 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N49" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
         <v>1.92</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AB49" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="M50" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.73</v>
+        <v>5.2</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N68" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="M70" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB70" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M79" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N80" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="M82" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="M83" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N83" t="n">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.02</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="M42" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="N42" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.03</v>
+        <v>3.05</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>3.19</v>
       </c>
       <c r="N48" t="n">
-        <v>6.9</v>
+        <v>1.85</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="M49" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N49" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.05</v>
+        <v>1.69</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N50" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB50" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.9</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.85</v>
+        <v>1.49</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M58" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>7.3</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>22</v>
+        <v>3.47</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M74" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N74" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.78</v>
+        <v>2.34</v>
       </c>
       <c r="M77" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N77" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N78" t="n">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>1.88</v>
+        <v>3.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="M81" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M83" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N83" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M91" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N92" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
         <v>4.4</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.61</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3.09</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.42</v>
+        <v>6.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.85</v>
+        <v>2.61</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N36" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M37" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.53</v>
+        <v>3.05</v>
       </c>
       <c r="M42" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6.2</v>
+        <v>2.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,14 +5776,14 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.05</v>
+        <v>2.03</v>
       </c>
       <c r="M45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N45" t="n">
         <v>3.4</v>
       </c>
-      <c r="N45" t="n">
-        <v>2.25</v>
-      </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.92</v>
+        <v>2.85</v>
       </c>
       <c r="M47" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.75</v>
+        <v>1.35</v>
       </c>
       <c r="M48" t="n">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>1.85</v>
+        <v>7.6</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.69</v>
+        <v>4</v>
       </c>
       <c r="M50" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="N50" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N52" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="M72" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB72" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M75" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N75" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="M78" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.78</v>
+        <v>3.56</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>3.85</v>
+        <v>1.88</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="M80" t="n">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="N80" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>2.3</v>
+        <v>3.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.56</v>
+        <v>1.72</v>
       </c>
       <c r="M83" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N83" t="n">
-        <v>1.88</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="M14" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
         <v>4.4</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N33" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="M34" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.61</v>
+        <v>3.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.39</v>
+        <v>4</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M38" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.75</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
       <c r="N39" t="n">
-        <v>1.85</v>
+        <v>7.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="M40" t="n">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="N40" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.69</v>
+        <v>2.5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5586,7 +5586,7 @@
         <v>1.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.03</v>
+        <v>2.85</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.35</v>
+        <v>2.61</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>3.09</v>
       </c>
       <c r="N48" t="n">
-        <v>7.6</v>
+        <v>2.42</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4</v>
+        <v>1.39</v>
       </c>
       <c r="M50" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="N50" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="M51" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="N51" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="M52" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N52" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="N54" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>7.3</v>
+        <v>3.85</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>3.47</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="M69" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB69" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M76" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="M77" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="N77" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,55 +9703,55 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N78" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
         <v>2.3</v>
       </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AB78" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.56</v>
+        <v>1.78</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>1.88</v>
+        <v>3.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.78</v>
+        <v>3.56</v>
       </c>
       <c r="M81" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>3.85</v>
+        <v>1.88</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.06</v>
+        <v>2.65</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="M83" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G89" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.92</v>
+        <v>1.49</v>
       </c>
       <c r="M33" t="n">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>1.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="N40" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,14 +5419,14 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.05</v>
+        <v>2.03</v>
       </c>
       <c r="M42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N42" t="n">
         <v>3.4</v>
       </c>
-      <c r="N42" t="n">
-        <v>2.25</v>
-      </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N44" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.26</v>
+        <v>6.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.03</v>
+        <v>1.35</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.61</v>
+        <v>3.05</v>
       </c>
       <c r="M48" t="n">
-        <v>3.09</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.69</v>
+        <v>3.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>4.5</v>
+        <v>2.01</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.39</v>
+        <v>4</v>
       </c>
       <c r="M50" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N50" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.75</v>
+        <v>1.53</v>
       </c>
       <c r="M51" t="n">
-        <v>3.19</v>
+        <v>4.2</v>
       </c>
       <c r="N51" t="n">
-        <v>1.85</v>
+        <v>6.2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.4</v>
+        <v>2.61</v>
       </c>
       <c r="M52" t="n">
-        <v>4.3</v>
+        <v>3.09</v>
       </c>
       <c r="N52" t="n">
-        <v>6.9</v>
+        <v>2.42</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.95</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="M54" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M58" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.13</v>
+        <v>1.92</v>
       </c>
       <c r="M59" t="n">
-        <v>7.3</v>
+        <v>3.85</v>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>3.47</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N66" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M67" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="M68" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB68" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N69" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M78" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N79" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="M80" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
-        <v>3.36</v>
+        <v>3.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N81" t="n">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N82" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N91" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M92" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.85</v>
+        <v>2.61</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N37" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="N40" t="n">
-        <v>6.1</v>
+        <v>1.85</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.03</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N42" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.75</v>
+        <v>1.35</v>
       </c>
       <c r="M44" t="n">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>7.6</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>6.9</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="M46" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.35</v>
+        <v>3.45</v>
       </c>
       <c r="M47" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>7.6</v>
+        <v>2.01</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.45</v>
+        <v>2.03</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>2.01</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="M50" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N50" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M51" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="N51" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7374,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M59" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N59" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD59" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N68" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="M69" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB69" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N77" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.56</v>
+        <v>2.34</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N78" t="n">
-        <v>1.88</v>
+        <v>2.92</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="M79" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>3.36</v>
+        <v>3.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N80" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M81" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N81" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="M82" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M91" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N92" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46025.125</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46025.22916666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46025.22916666666</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46025.23263888889</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
         <v>4.4</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>2.85</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>2.26</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="M35" t="n">
         <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB35" t="n">
         <v>1.9</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.61</v>
+        <v>3.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>2.01</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.75</v>
+        <v>1.71</v>
       </c>
       <c r="M40" t="n">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>1.85</v>
+        <v>4.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.92</v>
+        <v>3.05</v>
       </c>
       <c r="M41" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.35</v>
+        <v>3.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>3.19</v>
       </c>
       <c r="N44" t="n">
-        <v>7.6</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.45</v>
+        <v>1.69</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>2.01</v>
+        <v>4.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N48" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.03</v>
+        <v>2.61</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M50" t="n">
         <v>4.3</v>
       </c>
       <c r="N50" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="M68" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB68" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>2.1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N69" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M74" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N74" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="M77" t="n">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="N77" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="M78" t="n">
-        <v>2.85</v>
+        <v>3.32</v>
       </c>
       <c r="N78" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.06</v>
+        <v>2.65</v>
       </c>
       <c r="M83" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N83" t="n">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N91" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M92" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -704,7 +704,7 @@
         <v>3.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2</v>
+        <v>3.26</v>
       </c>
       <c r="N3" t="n">
-        <v>8.6</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
         <v>3.14</v>
       </c>
       <c r="T3" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.41</v>
+        <v>3.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.42</v>
+        <v>1.75</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46025.22916666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>3.26</v>
+        <v>5.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.48</v>
+        <v>1.69</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
         <v>3.14</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.48</v>
+        <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.25</v>
+        <v>2.41</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.75</v>
+        <v>3.42</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46025.22916666666</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
         <v>2.7</v>
@@ -1064,7 +1064,7 @@
         <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>3.08</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="M18" t="n">
-        <v>3.39</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="M34" t="n">
         <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,14 +4586,14 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N35" t="n">
         <v>3.4</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,14 +4824,14 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N37" t="n">
         <v>3.45</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.01</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
-        <v>2.25</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M42" t="n">
         <v>4.3</v>
       </c>
       <c r="N42" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>3.05</v>
       </c>
       <c r="M43" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.75</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.19</v>
+        <v>3.85</v>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>6.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N45" t="n">
-        <v>6.1</v>
+        <v>1.98</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="M46" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N46" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.69</v>
+        <v>3.75</v>
       </c>
       <c r="M47" t="n">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="N47" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>1.8</v>
+        <v>6.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.61</v>
+        <v>1.39</v>
       </c>
       <c r="M49" t="n">
-        <v>3.09</v>
+        <v>4.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.42</v>
+        <v>6.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="M50" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="N50" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="M54" t="n">
-        <v>3.66</v>
+        <v>3.94</v>
       </c>
       <c r="N54" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="M55" t="n">
-        <v>3.94</v>
+        <v>3.66</v>
       </c>
       <c r="N55" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M60" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N60" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,16 +7606,16 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD60" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7838,16 +7838,16 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7957,10 +7957,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>7.4</v>
+        <v>1.29</v>
       </c>
       <c r="M66" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.29</v>
+        <v>7.4</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N67" t="n">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.73</v>
+        <v>5.2</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="N68" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M76" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="M77" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>2.92</v>
+        <v>2.3</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.72</v>
+        <v>3.56</v>
       </c>
       <c r="M78" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>4.2</v>
+        <v>1.88</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N79" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="M80" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
-        <v>3.36</v>
+        <v>3.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>3.56</v>
+        <v>2.06</v>
       </c>
       <c r="M81" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>1.88</v>
+        <v>2.98</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N82" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,55 +10298,55 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="M83" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N83" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
         <v>2.3</v>
       </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AB83" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M91" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N92" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -662,10 +662,10 @@
         <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -674,22 +674,22 @@
         <v>2.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -698,13 +698,13 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
         <v>3.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
@@ -713,10 +713,10 @@
         <v>2.94</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
         <v>2.7</v>
@@ -1046,16 +1046,16 @@
         <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>6.8</v>
+        <v>6.85</v>
       </c>
       <c r="W5" t="n">
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z5" t="n">
         <v>3.5</v>
@@ -1064,7 +1064,7 @@
         <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC5" t="n">
         <v>3.08</v>
@@ -1082,7 +1082,7 @@
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46025.23263888889</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46025.33333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="M17" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,16 +2489,16 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>5.7</v>
+        <v>3.72</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46025.4375</v>
@@ -3280,10 +3280,10 @@
         <v>3.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3405,64 +3405,64 @@
         <v>3.2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46025.4375</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.92</v>
+        <v>4.34</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>1.81</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46025.4375</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.4</v>
+        <v>1.58</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="N27" t="n">
-        <v>1.78</v>
+        <v>5.5</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46025.4375</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
         <v>4.4</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46025.45833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="N34" t="n">
-        <v>4.5</v>
+        <v>5.04</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46025.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>4.15</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.15</v>
+        <v>1.67</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.9</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.38</v>
+        <v>3.05</v>
       </c>
       <c r="M42" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>7.4</v>
+        <v>2.25</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.05</v>
+        <v>1.53</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.25</v>
+        <v>6.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="M44" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="N44" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="M45" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.49</v>
+        <v>2.61</v>
       </c>
       <c r="M46" t="n">
-        <v>3.7</v>
+        <v>3.09</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>2.42</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.75</v>
+        <v>1.69</v>
       </c>
       <c r="M47" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.39</v>
+        <v>3.75</v>
       </c>
       <c r="M49" t="n">
-        <v>4.1</v>
+        <v>3.19</v>
       </c>
       <c r="N49" t="n">
-        <v>6.4</v>
+        <v>1.85</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="M50" t="n">
-        <v>3.28</v>
+        <v>3.85</v>
       </c>
       <c r="N50" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.85</v>
+        <v>1.92</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N52" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M58" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N58" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD58" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7612,10 +7612,10 @@
         <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3</v>
+        <v>4.15</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46025.5625</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="M62" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46025.5625</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="M63" t="n">
         <v>2.95</v>
       </c>
       <c r="N63" t="n">
-        <v>4.15</v>
+        <v>2.85</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46025.5625</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M64" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N64" t="n">
         <v>4.15</v>
       </c>
-      <c r="M64" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1.75</v>
-      </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA64" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46025.5625</v>
@@ -8165,40 +8165,40 @@
         <v>5</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA65" t="n">
         <v>2.2</v>
@@ -8207,22 +8207,22 @@
         <v>1.6</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>46025.5625</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.05</v>
+        <v>5.2</v>
       </c>
       <c r="M69" t="n">
-        <v>3.27</v>
+        <v>4.3</v>
       </c>
       <c r="N69" t="n">
-        <v>3.62</v>
+        <v>1.6</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.78</v>
+        <v>1.22</v>
       </c>
       <c r="M75" t="n">
-        <v>3.41</v>
+        <v>5.8</v>
       </c>
       <c r="N75" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.22</v>
+        <v>2.78</v>
       </c>
       <c r="M76" t="n">
-        <v>5.8</v>
+        <v>3.41</v>
       </c>
       <c r="N76" t="n">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,55 +9584,55 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="N77" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
         <v>2.3</v>
       </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AB77" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.56</v>
+        <v>2.65</v>
       </c>
       <c r="M78" t="n">
         <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="M79" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>3.36</v>
+        <v>1.88</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N80" t="n">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="M81" t="n">
         <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="M83" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N91" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M92" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -796,16 +796,16 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
         <v>6.45</v>
@@ -826,13 +826,13 @@
         <v>1.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC3" t="n">
         <v>3.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
         <v>1.68</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="M4" t="n">
         <v>5.2</v>
       </c>
       <c r="N4" t="n">
-        <v>8.6</v>
+        <v>10.7</v>
       </c>
       <c r="O4" t="n">
         <v>1.69</v>
@@ -936,16 +936,16 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="AA4" t="n">
         <v>1.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AC4" t="n">
         <v>2.41</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46025.35416666666</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46025.375</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V12" t="n">
         <v>4.4</v>
       </c>
-      <c r="N12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46025.38541666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46025.39583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.42</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46025.39583333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46025.41666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>4.15</v>
+        <v>3.36</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>3.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46025.41666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46025.41666666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.92</v>
+        <v>1.51</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.94</v>
+        <v>5.27</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46025.41666666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,28 +3158,28 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.96</v>
+        <v>4.34</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N23" t="n">
-        <v>3.72</v>
+        <v>1.81</v>
       </c>
       <c r="O23" t="n">
-        <v>2.63</v>
+        <v>5.33</v>
       </c>
       <c r="P23" t="n">
         <v>1.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.72</v>
+        <v>2.47</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T23" t="n">
         <v>3.28</v>
@@ -3188,7 +3188,7 @@
         <v>1.26</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
@@ -3203,28 +3203,28 @@
         <v>2.52</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46025.4375</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>2.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V24" t="n">
+        <v>9</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.21</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46025.4375</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="O25" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="P25" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>4.72</v>
       </c>
       <c r="R25" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S25" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="T25" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U25" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W25" t="n">
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46025.4375</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.34</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="N26" t="n">
-        <v>1.81</v>
+        <v>2.21</v>
       </c>
       <c r="O26" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46025.4375</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46025.45833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46025.45833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
         <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE30" t="n">
         <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46025.45833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.5</v>
+        <v>1.33</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>4.95</v>
       </c>
       <c r="N32" t="n">
-        <v>1.98</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46025.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.03</v>
+        <v>4.23</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46025.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="M34" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="N34" t="n">
-        <v>5.04</v>
+        <v>5.8</v>
       </c>
       <c r="O34" t="n">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>6.15</v>
       </c>
       <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.42</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V34" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE34" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.03</v>
+        <v>2.59</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46025.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.15</v>
+        <v>1.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA35" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF35" t="n">
         <v>1.88</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46025.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46025.5</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>3.5</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="N39" t="n">
-        <v>6.4</v>
+        <v>1.98</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46025.5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46025.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46025.5</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46025.5</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46025.5</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M44" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="N44" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46025.5</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.85</v>
+        <v>3.39</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="N45" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46025.5</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.61</v>
+        <v>4.17</v>
       </c>
       <c r="M46" t="n">
-        <v>3.09</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46025.5</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.69</v>
+        <v>2.82</v>
       </c>
       <c r="M47" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="N47" t="n">
-        <v>4.5</v>
+        <v>2.31</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46025.5</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46025.5</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="M49" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="N49" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46025.5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="M50" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="N50" t="n">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46025.5</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46025.5</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="M52" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="N52" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46025.5</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46025.51041666666</v>
@@ -6856,40 +6856,40 @@
         <v>5.7</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA54" t="n">
         <v>1.91</v>
@@ -6898,22 +6898,22 @@
         <v>1.83</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI54" s="3" t="n">
         <v>46025.51041666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.7</v>
+        <v>3.17</v>
       </c>
       <c r="M55" t="n">
-        <v>3.66</v>
+        <v>2.85</v>
       </c>
       <c r="N55" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.89</v>
+        <v>2.54</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46025.51041666666</v>
@@ -7094,40 +7094,40 @@
         <v>4</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA56" t="n">
         <v>2</v>
@@ -7136,22 +7136,22 @@
         <v>1.72</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46025.52083333334</v>
@@ -7332,46 +7332,46 @@
         <v>22</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC58" t="n">
         <v>2.1</v>
@@ -7380,16 +7380,16 @@
         <v>1.65</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46025.54166666666</v>
@@ -7451,40 +7451,40 @@
         <v>3.47</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA59" t="n">
         <v>1.65</v>
@@ -7493,22 +7493,22 @@
         <v>2.25</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46025.54166666666</v>
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N61" t="n">
         <v>4.15</v>
       </c>
-      <c r="M61" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1.75</v>
-      </c>
       <c r="O61" t="n">
-        <v>5.26</v>
+        <v>2.68</v>
       </c>
       <c r="P61" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.35</v>
+        <v>5.17</v>
       </c>
       <c r="R61" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB61" t="n">
         <v>1.4</v>
       </c>
-      <c r="S61" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V61" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X61" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC61" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.14</v>
+        <v>1.69</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46025.5625</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3</v>
+        <v>4.15</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="O62" t="n">
-        <v>3.9</v>
+        <v>5.26</v>
       </c>
       <c r="P62" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="R62" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S62" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="T62" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="U62" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V62" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y62" t="n">
         <v>1.28</v>
       </c>
-      <c r="V62" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X62" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1.35</v>
-      </c>
       <c r="Z62" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46025.5625</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="M64" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="N64" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="O64" t="n">
-        <v>2.68</v>
+        <v>2.28</v>
       </c>
       <c r="P64" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.17</v>
+        <v>5.86</v>
       </c>
       <c r="R64" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="S64" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="T64" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="U64" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="V64" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="W64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X64" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC64" t="n">
-        <v>5</v>
+        <v>3.98</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46025.5625</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,28 +8156,28 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>5</v>
+        <v>2.18</v>
       </c>
       <c r="O65" t="n">
-        <v>2.28</v>
+        <v>3.9</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.86</v>
+        <v>2.93</v>
       </c>
       <c r="R65" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S65" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T65" t="n">
         <v>3.14</v>
@@ -8186,19 +8186,19 @@
         <v>1.28</v>
       </c>
       <c r="V65" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X65" t="n">
         <v>1.02</v>
       </c>
-      <c r="X65" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y65" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AA65" t="n">
         <v>2.2</v>
@@ -8207,22 +8207,22 @@
         <v>1.6</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE65" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH65" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>46025.5625</v>
@@ -8284,40 +8284,40 @@
         <v>10</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA66" t="n">
         <v>1.87</v>
@@ -8326,22 +8326,22 @@
         <v>1.87</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46025.58333333334</v>
@@ -8403,40 +8403,40 @@
         <v>1.4</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA67" t="n">
         <v>1.7</v>
@@ -8445,22 +8445,22 @@
         <v>2.02</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>46025.58333333334</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46025.60416666666</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.2</v>
+        <v>1.73</v>
       </c>
       <c r="M69" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="M70" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N70" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>46025.60416666666</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,73 +8870,73 @@
         </is>
       </c>
       <c r="L71" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M71" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O71" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q71" t="n">
         <v>2.05</v>
       </c>
-      <c r="M71" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N71" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI71" s="3" t="n">
         <v>46025.60416666666</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.34</v>
+        <v>3.56</v>
       </c>
       <c r="M77" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N78" t="n">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.56</v>
+        <v>2.65</v>
       </c>
       <c r="M79" t="n">
         <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="M80" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
-        <v>3.36</v>
+        <v>3.85</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.78</v>
+        <v>2.34</v>
       </c>
       <c r="M81" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N81" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M84" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N84" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="M85" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N85" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="M91" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N91" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="N92" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -662,10 +662,10 @@
         <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -704,7 +704,7 @@
         <v>3.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
         <v>2.7</v>
@@ -1064,7 +1064,7 @@
         <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
         <v>3.08</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
         <v>3.2</v>
@@ -1388,13 +1388,13 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
         <v>2.99</v>
@@ -1412,16 +1412,16 @@
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC8" t="n">
         <v>3.88</v>
@@ -1430,16 +1430,16 @@
         <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46025.33333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="O13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U13" t="n">
         <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.72</v>
+        <v>3.03</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46025.39583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>4.42</v>
+        <v>4.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="P14" t="n">
         <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.5</v>
+        <v>5.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V14" t="n">
-        <v>6.7</v>
+        <v>5.85</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.03</v>
+        <v>2.69</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46025.39583333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46025.41666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46025.41666666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="M19" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>5.27</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Q19" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V19" t="n">
         <v>4.5</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V19" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.94</v>
+        <v>4.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.74</v>
+        <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.62</v>
+        <v>2.28</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46025.41666666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,70 +2801,70 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
         <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
         <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
         <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
         <v>1.91</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.36</v>
       </c>
       <c r="N21" t="n">
-        <v>5.27</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.29</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>2.59</v>
       </c>
       <c r="T21" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.95</v>
+        <v>2.94</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>1.74</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.28</v>
+        <v>3.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46025.41666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.34</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>5.33</v>
+        <v>2.92</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.47</v>
+        <v>4.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="T23" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V23" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="W23" t="n">
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.14</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46025.4375</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46025.4375</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
         <v>2.63</v>
@@ -3441,10 +3441,10 @@
         <v>2.52</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
         <v>4.3</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.21</v>
+        <v>1.78</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46025.4375</v>
@@ -3634,28 +3634,28 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="P27" t="n">
         <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.34</v>
+        <v>6.79</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
         <v>3.04</v>
@@ -3670,7 +3670,7 @@
         <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
         <v>1.33</v>
@@ -3679,28 +3679,28 @@
         <v>2.83</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46025.4375</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.69</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.47</v>
+        <v>4.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46025.45833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3875,70 +3875,70 @@
         <v>1.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q29" t="n">
-        <v>5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V29" t="n">
-        <v>8</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46025.45833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="T30" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
         <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE30" t="n">
         <v>1.86</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46025.45833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46025.5</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46025.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="N34" t="n">
-        <v>5.8</v>
+        <v>3.28</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.15</v>
+        <v>4.21</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S34" t="n">
-        <v>3.12</v>
+        <v>2.53</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="V34" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="AA34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB34" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AC34" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.59</v>
+        <v>1.59</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46025.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>1.34</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="O35" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="P35" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="T35" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V35" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="W35" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.12</v>
+        <v>3.74</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AC35" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46025.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46025.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46025.5</v>
@@ -4943,16 +4943,16 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="M38" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>5.04</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="P38" t="n">
         <v>2.14</v>
@@ -4967,7 +4967,7 @@
         <v>2.53</v>
       </c>
       <c r="T38" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="U38" t="n">
         <v>1.32</v>
@@ -4988,25 +4988,25 @@
         <v>2.92</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AC38" t="n">
         <v>3.48</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AF38" t="n">
         <v>1.73</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
         <v>2.03</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="M39" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="P39" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S39" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T39" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V39" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.95</v>
+        <v>3.12</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46025.5</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>2.53</v>
+        <v>5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.42</v>
+        <v>2.25</v>
       </c>
       <c r="P40" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.1</v>
+        <v>5.31</v>
       </c>
       <c r="R40" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="T40" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U40" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V40" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W40" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46025.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="M41" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="N41" t="n">
-        <v>6.2</v>
+        <v>4.22</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="R41" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S41" t="n">
         <v>2.82</v>
       </c>
       <c r="T41" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="U41" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V41" t="n">
-        <v>5.95</v>
+        <v>6.6</v>
       </c>
       <c r="W41" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB41" t="n">
+      <c r="AE41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF41" t="n">
         <v>1.92</v>
       </c>
-      <c r="AC41" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE41" t="n">
+      <c r="AG41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.93</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.35</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46025.5</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.1</v>
+        <v>4.24</v>
       </c>
       <c r="M42" t="n">
-        <v>3.14</v>
+        <v>3.69</v>
       </c>
       <c r="N42" t="n">
-        <v>3.28</v>
+        <v>1.78</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>5.21</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.21</v>
+        <v>2.28</v>
       </c>
       <c r="R42" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S42" t="n">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="T42" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U42" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="V42" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.59</v>
+        <v>1.13</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46025.5</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.61</v>
+        <v>3.52</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="N43" t="n">
-        <v>4.7</v>
+        <v>1.92</v>
       </c>
       <c r="O43" t="n">
-        <v>2.2</v>
+        <v>4.31</v>
       </c>
       <c r="P43" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.5</v>
+        <v>2.52</v>
       </c>
       <c r="R43" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S43" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U43" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V43" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA43" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF43" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF43" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG43" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46025.5</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.34</v>
+        <v>3.5</v>
       </c>
       <c r="M44" t="n">
-        <v>4.25</v>
+        <v>3.24</v>
       </c>
       <c r="N44" t="n">
-        <v>7.8</v>
+        <v>1.98</v>
       </c>
       <c r="O44" t="n">
-        <v>1.88</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q44" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q44" t="n">
-        <v>7</v>
-      </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S44" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="T44" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="U44" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V44" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG44" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z44" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH44" t="n">
-        <v>2.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46025.5</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.39</v>
+        <v>3.11</v>
       </c>
       <c r="M45" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="N45" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O45" t="n">
-        <v>4.32</v>
+        <v>3.84</v>
       </c>
       <c r="P45" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="Q45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T45" t="n">
         <v>2.66</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.96</v>
-      </c>
       <c r="U45" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="V45" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="W45" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AC45" t="n">
-        <v>3.65</v>
+        <v>2.94</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46025.5</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.17</v>
+        <v>1.32</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="N46" t="n">
-        <v>1.77</v>
+        <v>10</v>
       </c>
       <c r="O46" t="n">
-        <v>4.95</v>
+        <v>1.82</v>
       </c>
       <c r="P46" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.36</v>
+        <v>7.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S46" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="T46" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="U46" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="V46" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.82</v>
+        <v>2.21</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.16</v>
+        <v>3.14</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46025.5</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.82</v>
+        <v>1.25</v>
       </c>
       <c r="M47" t="n">
-        <v>3.58</v>
+        <v>5.37</v>
       </c>
       <c r="N47" t="n">
-        <v>2.31</v>
+        <v>10</v>
       </c>
       <c r="O47" t="n">
-        <v>3.48</v>
+        <v>1.75</v>
       </c>
       <c r="P47" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R47" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S47" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="T47" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U47" t="n">
         <v>1.46</v>
       </c>
       <c r="V47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W47" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
         <v>1.22</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB47" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE47" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC47" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF47" t="n">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.37</v>
+        <v>3.24</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46025.5</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.73</v>
+        <v>4.23</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N48" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="O48" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="P48" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="R48" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T48" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U48" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="W48" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.65</v>
+        <v>3.24</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.04</v>
+        <v>1.2</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46025.5</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,37 +6252,37 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>2.25</v>
+        <v>3.62</v>
       </c>
       <c r="O49" t="n">
-        <v>3.64</v>
+        <v>2.61</v>
       </c>
       <c r="P49" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.88</v>
+        <v>4.7</v>
       </c>
       <c r="R49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U49" t="n">
         <v>1.35</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V49" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="W49" t="n">
         <v>1.08</v>
@@ -6291,34 +6291,34 @@
         <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z49" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AC49" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AG49" t="n">
         <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46025.5</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,34 +6371,34 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="M50" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O50" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="P50" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>7.55</v>
+        <v>6.15</v>
       </c>
       <c r="R50" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S50" t="n">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="T50" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U50" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V50" t="n">
         <v>6.2</v>
@@ -6407,37 +6407,37 @@
         <v>1.09</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z50" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46025.5</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,73 +6490,73 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.66</v>
+        <v>2.46</v>
       </c>
       <c r="M51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z51" t="n">
         <v>3.6</v>
       </c>
-      <c r="N51" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V51" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>3.48</v>
-      </c>
       <c r="AA51" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AI51" s="3" t="n">
         <v>46025.5</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,73 +6609,73 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.44</v>
+        <v>2.82</v>
       </c>
       <c r="M52" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="N52" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="O52" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="P52" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="R52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V52" t="n">
+        <v>6</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD52" t="n">
         <v>1.36</v>
       </c>
-      <c r="S52" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V52" t="n">
-        <v>7</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y52" t="n">
+      <c r="AE52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG52" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z52" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH52" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="AI52" s="3" t="n">
         <v>46025.5</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,73 +6728,73 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.7</v>
+        <v>3.17</v>
       </c>
       <c r="M53" t="n">
-        <v>3.66</v>
+        <v>2.85</v>
       </c>
       <c r="N53" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="O53" t="n">
-        <v>2.35</v>
+        <v>3.98</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="R53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V53" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH53" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U53" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V53" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.93</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46025.51041666666</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.17</v>
+        <v>1.7</v>
       </c>
       <c r="M55" t="n">
-        <v>2.85</v>
+        <v>3.66</v>
       </c>
       <c r="N55" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="O55" t="n">
-        <v>3.98</v>
+        <v>2.35</v>
       </c>
       <c r="P55" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="R55" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S55" t="n">
-        <v>2.36</v>
+        <v>2.81</v>
       </c>
       <c r="T55" t="n">
-        <v>3.58</v>
+        <v>2.86</v>
       </c>
       <c r="U55" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1.28</v>
       </c>
-      <c r="V55" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE55" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46025.51041666666</v>
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="M56" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="O56" t="n">
         <v>2.7</v>
@@ -7106,10 +7106,10 @@
         <v>1.37</v>
       </c>
       <c r="S56" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T56" t="n">
-        <v>3.01</v>
+        <v>2.94</v>
       </c>
       <c r="U56" t="n">
         <v>1.35</v>
@@ -7127,13 +7127,13 @@
         <v>1.28</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AC56" t="n">
         <v>3.38</v>
@@ -7148,7 +7148,7 @@
         <v>1.9</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH56" t="n">
         <v>1.78</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V58" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="W58" t="n">
         <v>1.13</v>
       </c>
-      <c r="M58" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N58" t="n">
-        <v>22</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P58" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S58" t="n">
-        <v>4</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V58" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X58" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z58" t="n">
         <v>4.7</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.98</v>
+        <v>1.53</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AH58" t="n">
-        <v>5.85</v>
+        <v>1.89</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46025.54166666666</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="M59" t="n">
-        <v>3.85</v>
+        <v>7.3</v>
       </c>
       <c r="N59" t="n">
-        <v>3.47</v>
+        <v>22</v>
       </c>
       <c r="O59" t="n">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="P59" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.88</v>
+        <v>16.5</v>
       </c>
       <c r="R59" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S59" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T59" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="U59" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V59" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="W59" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X59" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z59" t="n">
         <v>4.7</v>
       </c>
       <c r="AA59" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD59" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB59" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AE59" t="n">
-        <v>1.53</v>
+        <v>2.98</v>
       </c>
       <c r="AF59" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.89</v>
+        <v>5.85</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46025.54166666666</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="M61" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>4.15</v>
+        <v>2.18</v>
       </c>
       <c r="O61" t="n">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="P61" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.17</v>
+        <v>2.93</v>
       </c>
       <c r="R61" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="S61" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="T61" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="U61" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="V61" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W61" t="n">
         <v>1.01</v>
       </c>
       <c r="X61" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC61" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46025.5625</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,73 +7799,73 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.15</v>
+        <v>2.4</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N62" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="O62" t="n">
-        <v>5.26</v>
+        <v>3.6</v>
       </c>
       <c r="P62" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.35</v>
+        <v>3.28</v>
       </c>
       <c r="R62" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="S62" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="T62" t="n">
-        <v>2.92</v>
+        <v>3.58</v>
       </c>
       <c r="U62" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="V62" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W62" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X62" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AA62" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.5</v>
+        <v>4.95</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46025.5625</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.4</v>
+        <v>4.15</v>
       </c>
       <c r="M63" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="O63" t="n">
-        <v>3.6</v>
+        <v>5.26</v>
       </c>
       <c r="P63" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V63" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE63" t="n">
         <v>1.86</v>
       </c>
-      <c r="Q63" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T63" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V63" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X63" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AF63" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46025.5625</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="M64" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="N64" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V64" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC64" t="n">
         <v>5</v>
       </c>
-      <c r="O64" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="P64" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T64" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V64" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>3.98</v>
-      </c>
       <c r="AD64" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH64" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46025.5625</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,28 +8156,28 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.18</v>
+        <v>5</v>
       </c>
       <c r="O65" t="n">
-        <v>3.9</v>
+        <v>2.31</v>
       </c>
       <c r="P65" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.93</v>
+        <v>5.92</v>
       </c>
       <c r="R65" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S65" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="T65" t="n">
         <v>3.14</v>
@@ -8186,19 +8186,19 @@
         <v>1.28</v>
       </c>
       <c r="V65" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X65" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AA65" t="n">
         <v>2.2</v>
@@ -8207,22 +8207,22 @@
         <v>1.6</v>
       </c>
       <c r="AC65" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="AI65" s="3" t="n">
         <v>46025.5625</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="M68" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N68" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="O68" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="P68" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Q68" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T68" t="n">
         <v>2.5</v>
       </c>
-      <c r="R68" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S68" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T68" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U68" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V68" t="n">
-        <v>6.4</v>
+        <v>5.75</v>
       </c>
       <c r="W68" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X68" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z68" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB68" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46025.60416666666</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,73 +8751,73 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="M70" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="N70" t="n">
-        <v>3.62</v>
+        <v>2.16</v>
       </c>
       <c r="O70" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="P70" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.72</v>
+        <v>2.5</v>
       </c>
       <c r="R70" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S70" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="T70" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="U70" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="V70" t="n">
-        <v>6.05</v>
+        <v>6.4</v>
       </c>
       <c r="W70" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X70" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z70" t="n">
-        <v>4.37</v>
+        <v>3.75</v>
       </c>
       <c r="AA70" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE70" t="n">
         <v>1.65</v>
       </c>
-      <c r="AB70" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AF70" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>46025.60416666666</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,73 +8870,73 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.2</v>
+        <v>1.73</v>
       </c>
       <c r="M71" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="O71" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="P71" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="R71" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S71" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="T71" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="U71" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V71" t="n">
-        <v>6.25</v>
+        <v>8.1</v>
       </c>
       <c r="W71" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X71" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="Z71" t="n">
-        <v>4.15</v>
+        <v>2.78</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AC71" t="n">
-        <v>2.68</v>
+        <v>3.72</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AF71" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AI71" s="3" t="n">
         <v>46025.60416666666</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>46025.60416666666</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,73 +9108,73 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="M73" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="N73" t="n">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>46025.625</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>46025.625</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.56</v>
+        <v>2.65</v>
       </c>
       <c r="M77" t="n">
         <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.05</v>
+        <v>3.56</v>
       </c>
       <c r="M78" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>3.36</v>
+        <v>1.88</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.65</v>
+        <v>2.06</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>2.3</v>
+        <v>2.98</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="N80" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="M82" t="n">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="M83" t="n">
         <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10426,40 +10426,40 @@
         <v>3.7</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA84" t="n">
         <v>2.2</v>
@@ -10468,22 +10468,22 @@
         <v>1.6</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI84" s="3" t="n">
         <v>46025.6875</v>
@@ -10545,40 +10545,40 @@
         <v>3.45</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA85" t="n">
         <v>2.4</v>
@@ -10587,22 +10587,22 @@
         <v>1.5</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI85" s="3" t="n">
         <v>46025.6875</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11250,73 +11250,73 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M91" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N91" t="n">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X91" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI91" s="3" t="n">
         <v>46025.72916666666</v>
@@ -11378,40 +11378,40 @@
         <v>4.3</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U92" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V92" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W92" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA92" t="n">
         <v>1.9</v>
@@ -11420,22 +11420,22 @@
         <v>1.8</v>
       </c>
       <c r="AC92" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD92" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG92" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH92" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI92" s="3" t="n">
         <v>46025.72916666666</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G95" t="n">

--- a/jogos_2026-01-03.xlsx
+++ b/jogos_2026-01-03.xlsx
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="P9" t="n">
         <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.6</v>
+        <v>4.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
         <v>2.83</v>
@@ -1522,7 +1522,7 @@
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.06</v>
@@ -1534,25 +1534,25 @@
         <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AD9" t="n">
         <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
         <v>1.29</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46025.375</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46025.375</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>6.44</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.92</v>
@@ -1900,10 +1900,10 @@
         <v>2.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE12" t="n">
         <v>1.63</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
         <v>2.4</v>
@@ -2013,10 +2013,10 @@
         <v>3.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>3.03</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="N14" t="n">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>2.22</v>
@@ -2132,10 +2132,10 @@
         <v>3.84</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC14" t="n">
         <v>2.69</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46025.41666666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46025.41666666666</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="N19" t="n">
-        <v>5.27</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
         <v>2.04</v>
@@ -2721,7 +2721,7 @@
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z19" t="n">
         <v>4.95</v>
@@ -2733,10 +2733,10 @@
         <v>2.35</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
         <v>1.56</v>
@@ -2920,19 +2920,19 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="M21" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="O21" t="n">
         <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q21" t="n">
         <v>4.5</v>
@@ -2944,13 +2944,13 @@
         <v>2.59</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
@@ -2959,22 +2959,22 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC21" t="n">
         <v>3.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
         <v>1.85</v>
@@ -2986,7 +2986,7 @@
         <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46025.41666666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>3.15</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46025.4375</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,49 +3277,49 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.15</v>
+        <v>1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA24" t="n">
         <v>2.3</v>
@@ -3328,22 +3328,22 @@
         <v>1.55</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46025.4375</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,28 +3396,28 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.92</v>
+        <v>4.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>1.78</v>
       </c>
       <c r="O25" t="n">
-        <v>2.63</v>
+        <v>5.33</v>
       </c>
       <c r="P25" t="n">
         <v>1.93</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.72</v>
+        <v>2.47</v>
       </c>
       <c r="R25" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S25" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T25" t="n">
         <v>3.28</v>
@@ -3426,7 +3426,7 @@
         <v>1.26</v>
       </c>
       <c r="V25" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>1.01</v>
@@ -3447,22 +3447,22 @@
         <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.68</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46025.4375</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.4</v>
+        <v>1.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.78</v>
+        <v>5.7</v>
       </c>
       <c r="O26" t="n">
-        <v>5.33</v>
+        <v>2.14</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S26" t="n">
         <v>2.47</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.34</v>
-      </c>
       <c r="T26" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V26" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.14</v>
+        <v>2.21</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46025.4375</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.14</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.79</v>
+        <v>4.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="T27" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U27" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V27" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.02</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46025.4375</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="P28" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.69</v>
+        <v>3.08</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.75</v>
+        <v>3.47</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46025.45833333334</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>2.5</v>
@@ -3890,10 +3890,10 @@
         <v>4.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
         <v>3.1</v>
@@ -3905,10 +3905,10 @@
         <v>6.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
         <v>1.31</v>
@@ -3917,16 +3917,16 @@
         <v>3.12</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
         <v>3.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE29" t="n">
         <v>1.86</v>
@@ -3935,7 +3935,7 @@
         <v>1.91</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
         <v>1.92</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
-        <v>2.28</v>
+        <v>2.59</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S30" t="n">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V30" t="n">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.08</v>
+        <v>2.53</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.47</v>
+        <v>5.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46025.45833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46025.5</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="M34" t="n">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>3.28</v>
+        <v>2.2</v>
       </c>
       <c r="O34" t="n">
-        <v>2.8</v>
+        <v>3.84</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.21</v>
+        <v>2.73</v>
       </c>
       <c r="R34" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="T34" t="n">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="U34" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="V34" t="n">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46025.5</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R35" t="n">
         <v>1.34</v>
       </c>
-      <c r="M35" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="N35" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>7</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S35" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U35" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
         <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="AA35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.7</v>
+        <v>1.22</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46025.5</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.61</v>
+        <v>4.15</v>
       </c>
       <c r="M36" t="n">
         <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>4.7</v>
+        <v>1.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.2</v>
+        <v>5.21</v>
       </c>
       <c r="P36" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2.28</v>
       </c>
-      <c r="Q36" t="n">
-        <v>5.5</v>
-      </c>
       <c r="R36" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="T36" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U36" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V36" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z36" t="n">
         <v>3.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.2</v>
+        <v>1.13</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46025.5</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M37" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="P37" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="S37" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="T37" t="n">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="U37" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="V37" t="n">
-        <v>5.95</v>
+        <v>7.7</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AC37" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46025.5</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="M38" t="n">
         <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="P38" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="R38" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S38" t="n">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="T38" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="U38" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V38" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46025.5</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46025.5</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O40" t="n">
         <v>1.75</v>
       </c>
-      <c r="M40" t="n">
+      <c r="P40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V40" t="n">
+        <v>5</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z40" t="n">
         <v>3.7</v>
       </c>
-      <c r="N40" t="n">
-        <v>5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V40" t="n">
-        <v>7</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AA40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE40" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AF40" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC40" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.04</v>
+        <v>3.24</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46025.5</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.52</v>
+        <v>3.24</v>
       </c>
       <c r="N41" t="n">
-        <v>4.22</v>
+        <v>1.98</v>
       </c>
       <c r="O41" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S41" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="T41" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="U41" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="V41" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
         <v>1.01</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z41" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE41" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.93</v>
+        <v>1.22</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46025.5</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,73 +5419,73 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.24</v>
+        <v>1.34</v>
       </c>
       <c r="M42" t="n">
-        <v>3.69</v>
+        <v>4.25</v>
       </c>
       <c r="N42" t="n">
-        <v>1.78</v>
+        <v>7.8</v>
       </c>
       <c r="O42" t="n">
-        <v>5.21</v>
+        <v>1.88</v>
       </c>
       <c r="P42" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="R42" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S42" t="n">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V42" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="W42" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
         <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.13</v>
+        <v>2.7</v>
       </c>
       <c r="AI42" s="3" t="n">
         <v>46025.5</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,73 +5538,73 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.52</v>
+        <v>1.47</v>
       </c>
       <c r="M43" t="n">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>1.92</v>
+        <v>6.2</v>
       </c>
       <c r="O43" t="n">
-        <v>4.31</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.52</v>
+        <v>6</v>
       </c>
       <c r="R43" t="n">
         <v>1.34</v>
       </c>
       <c r="S43" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="T43" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="U43" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V43" t="n">
-        <v>6.8</v>
+        <v>5.95</v>
       </c>
       <c r="W43" t="n">
         <v>1.07</v>
       </c>
       <c r="X43" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.14</v>
+        <v>3.55</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.22</v>
+        <v>2.35</v>
       </c>
       <c r="AI43" s="3" t="n">
         <v>46025.5</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="M44" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="P44" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R44" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="T44" t="n">
-        <v>3.08</v>
+        <v>2.47</v>
       </c>
       <c r="U44" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="V44" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
         <v>1.01</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z44" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AE44" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46025.5</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.11</v>
+        <v>1.61</v>
       </c>
       <c r="M45" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="N45" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="P45" t="n">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.73</v>
+        <v>5.5</v>
       </c>
       <c r="R45" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U45" t="n">
         <v>1.34</v>
       </c>
-      <c r="S45" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V45" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="W45" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.94</v>
+        <v>3.28</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46025.5</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.32</v>
+        <v>2.61</v>
       </c>
       <c r="M46" t="n">
-        <v>5.4</v>
+        <v>3.09</v>
       </c>
       <c r="N46" t="n">
-        <v>10</v>
+        <v>2.42</v>
       </c>
       <c r="O46" t="n">
-        <v>1.82</v>
+        <v>3.32</v>
       </c>
       <c r="P46" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="Q46" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S46" t="n">
-        <v>3.22</v>
+        <v>2.69</v>
       </c>
       <c r="T46" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="U46" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="V46" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X46" t="n">
         <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.14</v>
+        <v>1.38</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46025.5</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,73 +6014,73 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V47" t="n">
+        <v>7</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y47" t="n">
         <v>1.25</v>
       </c>
-      <c r="M47" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="N47" t="n">
-        <v>10</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="R47" t="n">
+      <c r="Z47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD47" t="n">
         <v>1.3</v>
       </c>
-      <c r="S47" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V47" t="n">
-        <v>5</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AE47" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AH47" t="n">
-        <v>3.24</v>
+        <v>2.04</v>
       </c>
       <c r="AI47" s="3" t="n">
         <v>46025.5</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,73 +6133,73 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.23</v>
+        <v>1.39</v>
       </c>
       <c r="M48" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N48" t="n">
-        <v>1.85</v>
+        <v>6.4</v>
       </c>
       <c r="O48" t="n">
-        <v>4.5</v>
+        <v>1.82</v>
       </c>
       <c r="P48" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V48" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB48" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="AC48" t="n">
         <v>2.45</v>
       </c>
-      <c r="R48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V48" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>3.24</v>
-      </c>
       <c r="AD48" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.2</v>
+        <v>3.14</v>
       </c>
       <c r="AI48" s="3" t="n">
         <v>46025.5</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>3.62</v>
+        <v>6.2</v>
       </c>
       <c r="O49" t="n">
-        <v>2.61</v>
+        <v>1.95</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.7</v>
+        <v>6.15</v>
       </c>
       <c r="R49" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S49" t="n">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="T49" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="U49" t="n">
-        <v>1.35</